--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_main.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_main.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="631">
   <si>
     <t xml:space="preserve">version</t>
   </si>
@@ -1191,6 +1191,12 @@
   </si>
   <si>
     <t xml:space="preserve">QuestExploration_AfterCrystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getAchievement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONEV</t>
   </si>
   <si>
     <t xml:space="preserve">bg_road</t>
@@ -2781,7 +2787,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="12.8">
@@ -2804,7 +2810,7 @@
         <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" ht="12.8">
@@ -2827,7 +2833,7 @@
         <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" ht="12.8">
@@ -2850,7 +2856,7 @@
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" ht="12.8">
@@ -2873,7 +2879,7 @@
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" ht="12.8">
@@ -2896,7 +2902,7 @@
         <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" ht="12.8">
@@ -2919,7 +2925,7 @@
         <v>37</v>
       </c>
       <c r="H11" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" ht="12.8">
@@ -2942,7 +2948,7 @@
         <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" ht="12.8">
@@ -2965,7 +2971,7 @@
         <v>45</v>
       </c>
       <c r="H13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" ht="12.8">
@@ -2988,7 +2994,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" ht="12.8">
@@ -3011,7 +3017,7 @@
         <v>53</v>
       </c>
       <c r="H15" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -4836,7 +4842,7 @@
         <v>92</v>
       </c>
       <c r="K35" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" ht="12.8">
@@ -4858,7 +4864,7 @@
         <v>94</v>
       </c>
       <c r="K37" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" ht="12.8">
@@ -4880,7 +4886,7 @@
         <v>96</v>
       </c>
       <c r="K39" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="40" ht="12.8">
@@ -4908,7 +4914,7 @@
         <v>99</v>
       </c>
       <c r="K41" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" ht="12.8">
@@ -5015,7 +5021,7 @@
         <v>117</v>
       </c>
       <c r="K54" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" s="5" customFormat="1" ht="12.8">
@@ -5301,7 +5307,7 @@
         <v>120</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -5564,7 +5570,7 @@
         <v>122</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -5827,7 +5833,7 @@
         <v>124</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -6629,7 +6635,7 @@
         <v>131</v>
       </c>
       <c r="K65" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="66" ht="32.8">
@@ -6643,7 +6649,7 @@
         <v>133</v>
       </c>
       <c r="K66" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" ht="12.8">
@@ -6665,7 +6671,7 @@
         <v>137</v>
       </c>
       <c r="K68" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69" ht="35.8">
@@ -6679,7 +6685,7 @@
         <v>139</v>
       </c>
       <c r="K69" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="70" ht="12.8">
@@ -6774,7 +6780,7 @@
         <v>144</v>
       </c>
       <c r="K80" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="82" ht="12.8">
@@ -7098,7 +7104,7 @@
         <v>150</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
@@ -7361,7 +7367,7 @@
         <v>152</v>
       </c>
       <c r="K96" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" ht="12.8">
@@ -7378,7 +7384,7 @@
         <v>154</v>
       </c>
       <c r="K97" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" ht="105.95">
@@ -7395,7 +7401,7 @@
         <v>156</v>
       </c>
       <c r="K98" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="99" ht="53.7">
@@ -7412,7 +7418,7 @@
         <v>158</v>
       </c>
       <c r="K99" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" ht="43.25">
@@ -7429,7 +7435,7 @@
         <v>160</v>
       </c>
       <c r="K100" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="101" ht="43.25">
@@ -7446,7 +7452,7 @@
         <v>162</v>
       </c>
       <c r="K101" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="102" ht="12.8">
@@ -7463,7 +7469,7 @@
         <v>164</v>
       </c>
       <c r="K102" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="103" ht="12.8">
@@ -7480,7 +7486,7 @@
         <v>166</v>
       </c>
       <c r="K103" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="104" ht="53.7">
@@ -7497,7 +7503,7 @@
         <v>168</v>
       </c>
       <c r="K104" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="105" ht="12.8">
@@ -7514,7 +7520,7 @@
         <v>170</v>
       </c>
       <c r="K105" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="106" ht="12.8">
@@ -7539,7 +7545,7 @@
         <v>172</v>
       </c>
       <c r="K107" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="108" ht="12.8">
@@ -8119,7 +8125,7 @@
         <v>177</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
@@ -8382,7 +8388,7 @@
         <v>179</v>
       </c>
       <c r="K119" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="120" ht="12.8">
@@ -8399,7 +8405,7 @@
         <v>181</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -8662,7 +8668,7 @@
         <v>183</v>
       </c>
       <c r="K121" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="122" ht="43.25">
@@ -8679,7 +8685,7 @@
         <v>185</v>
       </c>
       <c r="K122" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="123" ht="22.35">
@@ -8696,7 +8702,7 @@
         <v>187</v>
       </c>
       <c r="K123" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="124" ht="12.8">
@@ -8713,7 +8719,7 @@
         <v>189</v>
       </c>
       <c r="K124" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="125" ht="85.05">
@@ -8730,7 +8736,7 @@
         <v>191</v>
       </c>
       <c r="K125" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="126" ht="74.6">
@@ -8747,7 +8753,7 @@
         <v>193</v>
       </c>
       <c r="K126" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="127" ht="53.7">
@@ -8764,7 +8770,7 @@
         <v>195</v>
       </c>
       <c r="K127" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="128" ht="53.7">
@@ -8781,7 +8787,7 @@
         <v>197</v>
       </c>
       <c r="K128" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="129" ht="12.8">
@@ -9378,7 +9384,7 @@
         <v>177</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
@@ -9641,7 +9647,7 @@
         <v>202</v>
       </c>
       <c r="K140" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="141" ht="12.8">
@@ -9658,7 +9664,7 @@
         <v>204</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
@@ -9921,7 +9927,7 @@
         <v>206</v>
       </c>
       <c r="K142" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="143" ht="12.8">
@@ -9938,7 +9944,7 @@
         <v>208</v>
       </c>
       <c r="K143" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="144" ht="12.8">
@@ -9955,7 +9961,7 @@
         <v>210</v>
       </c>
       <c r="K144" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="145" ht="12.8">
@@ -10263,7 +10269,7 @@
         <v>214</v>
       </c>
       <c r="K150" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="151" ht="64.15">
@@ -10280,7 +10286,7 @@
         <v>216</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -10543,7 +10549,7 @@
         <v>218</v>
       </c>
       <c r="K152" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="153" ht="12.8">
@@ -10560,7 +10566,7 @@
         <v>220</v>
       </c>
       <c r="K153" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="154" ht="64.15">
@@ -10577,7 +10583,7 @@
         <v>222</v>
       </c>
       <c r="K154" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="155" ht="64.15">
@@ -10594,7 +10600,7 @@
         <v>224</v>
       </c>
       <c r="K155" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="156" ht="85.05">
@@ -10611,7 +10617,7 @@
         <v>226</v>
       </c>
       <c r="K156" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="157" ht="12.8">
@@ -10628,7 +10634,7 @@
         <v>228</v>
       </c>
       <c r="K157" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="158" ht="64.15">
@@ -10645,7 +10651,7 @@
         <v>230</v>
       </c>
       <c r="K158" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" ht="12.8">
@@ -10679,7 +10685,7 @@
         <v>232</v>
       </c>
       <c r="K160" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="161" ht="53.7">
@@ -10696,7 +10702,7 @@
         <v>234</v>
       </c>
       <c r="K161" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="162" ht="12.8">
@@ -12044,7 +12050,7 @@
         <v>241</v>
       </c>
       <c r="K174" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="175" ht="12.8">
@@ -12061,7 +12067,7 @@
         <v>244</v>
       </c>
       <c r="K175" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="176" s="5" customFormat="1" ht="12.8">
@@ -12084,7 +12090,7 @@
         <v>246</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
@@ -12353,7 +12359,7 @@
         <v>248</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
@@ -12622,7 +12628,7 @@
         <v>250</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
@@ -12891,7 +12897,7 @@
         <v>252</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
@@ -13160,7 +13166,7 @@
         <v>254</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
@@ -13930,7 +13936,7 @@
         <v>257</v>
       </c>
       <c r="K183" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184" ht="22.35">
@@ -13947,7 +13953,7 @@
         <v>259</v>
       </c>
       <c r="K184" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="185" ht="22.35">
@@ -13964,7 +13970,7 @@
         <v>261</v>
       </c>
       <c r="K185" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="186" ht="12.8">
@@ -13981,7 +13987,7 @@
         <v>263</v>
       </c>
       <c r="K186" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="187" ht="12.8">
@@ -14039,7 +14045,7 @@
         <v>266</v>
       </c>
       <c r="K191" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="192" ht="12.8">
@@ -14090,7 +14096,7 @@
         <v>269</v>
       </c>
       <c r="K201" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="202" ht="64.15">
@@ -14107,7 +14113,7 @@
         <v>271</v>
       </c>
       <c r="K202" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="205" ht="12.8">
@@ -15788,7 +15794,7 @@
         <v>282</v>
       </c>
       <c r="K236" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="237" ht="12.8">
@@ -15810,7 +15816,7 @@
         <v>284</v>
       </c>
       <c r="K238" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="239" ht="12.8">
@@ -15832,7 +15838,7 @@
         <v>286</v>
       </c>
       <c r="K240" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="241" ht="12.8">
@@ -15955,7 +15961,7 @@
         <v>294</v>
       </c>
       <c r="K255" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="256" ht="22.35">
@@ -15972,7 +15978,7 @@
         <v>296</v>
       </c>
       <c r="K256" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="257" ht="95.5">
@@ -15989,7 +15995,7 @@
         <v>298</v>
       </c>
       <c r="K257" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="258" ht="12.8">
@@ -16006,7 +16012,7 @@
         <v>300</v>
       </c>
       <c r="K258" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" ht="12.8">
@@ -16023,7 +16029,7 @@
         <v>302</v>
       </c>
       <c r="K259" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="260" ht="12.8">
@@ -16040,7 +16046,7 @@
         <v>304</v>
       </c>
       <c r="K260" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="261" ht="53.7">
@@ -16057,7 +16063,7 @@
         <v>306</v>
       </c>
       <c r="K261" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="262" ht="53.7">
@@ -16074,7 +16080,7 @@
         <v>308</v>
       </c>
       <c r="K262" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="263" ht="12.8">
@@ -16108,7 +16114,7 @@
         <v>310</v>
       </c>
       <c r="K264" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="265" ht="85.05">
@@ -16125,7 +16131,7 @@
         <v>312</v>
       </c>
       <c r="K265" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="266" ht="12.8">
@@ -16142,7 +16148,7 @@
         <v>314</v>
       </c>
       <c r="K266" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="267" ht="12.8">
@@ -16191,7 +16197,7 @@
         <v>319</v>
       </c>
       <c r="K271" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="273" ht="12.8">
@@ -16224,6 +16230,14 @@
       </c>
       <c r="E276" s="1" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="277" ht="12.8">
+      <c r="D277" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="282" ht="12.8">
@@ -16504,7 +16518,7 @@
         <v>128</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="289" ht="12.8">
@@ -16784,13 +16798,13 @@
         <v>83</v>
       </c>
       <c r="I291" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J291" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
@@ -17047,13 +17061,13 @@
         <v>84</v>
       </c>
       <c r="I293" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J293" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
@@ -17327,13 +17341,13 @@
         <v>86</v>
       </c>
       <c r="I295" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J295" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K295" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="296" ht="12.8">
@@ -17344,13 +17358,13 @@
         <v>87</v>
       </c>
       <c r="I296" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J296" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K296" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="297" ht="12.8">
@@ -17361,13 +17375,13 @@
         <v>88</v>
       </c>
       <c r="I297" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J297" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K297" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="298" ht="74.6">
@@ -17378,13 +17392,13 @@
         <v>89</v>
       </c>
       <c r="I298" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J298" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K298" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="299" ht="95.5">
@@ -17395,13 +17409,13 @@
         <v>90</v>
       </c>
       <c r="I299" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J299" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K299" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="300" ht="12.8">
@@ -17412,13 +17426,13 @@
         <v>91</v>
       </c>
       <c r="I300" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J300" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K300" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="301" ht="53.7">
@@ -17429,13 +17443,13 @@
         <v>92</v>
       </c>
       <c r="I301" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J301" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K301" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="302" ht="12.8">
@@ -17446,13 +17460,13 @@
         <v>93</v>
       </c>
       <c r="I302" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J302" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K302" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="303" ht="85.05">
@@ -17463,13 +17477,13 @@
         <v>94</v>
       </c>
       <c r="I303" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J303" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K303" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="304" ht="12.8">
@@ -17480,13 +17494,13 @@
         <v>95</v>
       </c>
       <c r="I304" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J304" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K304" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="305" ht="12.8">
@@ -17497,13 +17511,13 @@
         <v>96</v>
       </c>
       <c r="I305" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J305" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K305" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="306" ht="12.8">
@@ -17531,13 +17545,13 @@
         <v>98</v>
       </c>
       <c r="I307" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K307" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="308" ht="12.8">
@@ -17548,13 +17562,13 @@
         <v>99</v>
       </c>
       <c r="I308" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K308" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="309" ht="12.8">
@@ -17582,13 +17596,13 @@
         <v>101</v>
       </c>
       <c r="I310" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J310" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K310" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="311" ht="12.8">
@@ -17643,7 +17657,7 @@
         <v>86</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" ht="12.8">
@@ -17666,11 +17680,11 @@
         <v>106</v>
       </c>
       <c r="I323" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J323" s="4"/>
       <c r="K323" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
@@ -17924,10 +17938,10 @@
         <v>107</v>
       </c>
       <c r="I324" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K324" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="325" ht="12.8">
@@ -17935,10 +17949,10 @@
         <v>108</v>
       </c>
       <c r="I325" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K325" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
@@ -18192,10 +18206,10 @@
         <v>109</v>
       </c>
       <c r="I326" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K326" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="327" ht="22.35">
@@ -18203,10 +18217,10 @@
         <v>110</v>
       </c>
       <c r="I327" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K327" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="328" ht="12.8">
@@ -18214,10 +18228,10 @@
         <v>111</v>
       </c>
       <c r="I328" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K328" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="329" ht="12.8">
@@ -18225,10 +18239,10 @@
         <v>112</v>
       </c>
       <c r="I329" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K329" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="330" ht="12.8">
@@ -18252,7 +18266,7 @@
         <v>128</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="335" ht="12.8">
@@ -18260,7 +18274,7 @@
         <v>86</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="337" s="9" customFormat="1" ht="12.8">
@@ -18793,10 +18807,10 @@
         <v>113</v>
       </c>
       <c r="I339" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L339" s="1"/>
       <c r="M339" s="1"/>
@@ -19053,10 +19067,10 @@
         <v>114</v>
       </c>
       <c r="I340" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L340" s="1"/>
       <c r="M340" s="1"/>
@@ -19313,10 +19327,10 @@
         <v>115</v>
       </c>
       <c r="I341" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K341" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="342" ht="12.8">
@@ -19327,10 +19341,10 @@
         <v>116</v>
       </c>
       <c r="I342" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K342" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="343" ht="12.8">
@@ -19349,10 +19363,10 @@
         <v>117</v>
       </c>
       <c r="I344" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K344" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="345" ht="12.8">
@@ -19363,10 +19377,10 @@
         <v>118</v>
       </c>
       <c r="I345" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K345" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="346" ht="12.8">
@@ -19377,10 +19391,10 @@
         <v>119</v>
       </c>
       <c r="I346" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K346" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="347" ht="12.8">
@@ -19391,10 +19405,10 @@
         <v>120</v>
       </c>
       <c r="I347" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K347" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="348" ht="12.8">
@@ -19405,10 +19419,10 @@
         <v>121</v>
       </c>
       <c r="I348" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K348" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="349" ht="12.8">
@@ -19416,7 +19430,7 @@
         <v>86</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" ht="12.8">
@@ -19427,10 +19441,10 @@
         <v>122</v>
       </c>
       <c r="I350" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K350" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="351" s="9" customFormat="1" ht="12.8">
@@ -19952,7 +19966,7 @@
         <v>128</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="355" ht="12.8">
@@ -19963,7 +19977,7 @@
         <v>86</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="356" ht="12.8">
@@ -20241,10 +20255,10 @@
         <v>123</v>
       </c>
       <c r="I358" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K358" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="359" ht="12.8">
@@ -20509,7 +20523,7 @@
         <v>128</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="362" ht="12.8">
@@ -20520,7 +20534,7 @@
         <v>86</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="363" ht="12.8">
@@ -20545,11 +20559,11 @@
         <v>124</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J364" s="4"/>
       <c r="K364" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L364" s="1"/>
       <c r="M364" s="1"/>
@@ -20806,10 +20820,10 @@
         <v>125</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K365" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="366" ht="12.8">
@@ -20820,10 +20834,10 @@
         <v>126</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K366" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L366" s="1"/>
       <c r="M366" s="1"/>
@@ -21080,10 +21094,10 @@
         <v>127</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K367" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="368" ht="32.8">
@@ -21094,10 +21108,10 @@
         <v>128</v>
       </c>
       <c r="I368" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K368" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="369" ht="53.7">
@@ -21108,10 +21122,10 @@
         <v>129</v>
       </c>
       <c r="I369" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K369" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="370" ht="32.8">
@@ -21122,10 +21136,10 @@
         <v>130</v>
       </c>
       <c r="I370" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K370" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="371" ht="12.8">
@@ -21136,10 +21150,10 @@
         <v>131</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K371" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="372" ht="12.8">
@@ -21150,10 +21164,10 @@
         <v>132</v>
       </c>
       <c r="I372" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K372" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="373" ht="12.8">
@@ -21164,10 +21178,10 @@
         <v>133</v>
       </c>
       <c r="I373" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K373" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="374" ht="12.8">
@@ -21178,10 +21192,10 @@
         <v>134</v>
       </c>
       <c r="I374" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K374" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="375" ht="43.25">
@@ -21192,10 +21206,10 @@
         <v>135</v>
       </c>
       <c r="I375" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K375" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="376" ht="12.8">
@@ -21206,10 +21220,10 @@
         <v>136</v>
       </c>
       <c r="I376" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K376" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="377" ht="12.8">
@@ -21220,10 +21234,10 @@
         <v>137</v>
       </c>
       <c r="I377" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K377" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="378" ht="12.8">
@@ -21234,10 +21248,10 @@
         <v>138</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K378" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="379" ht="12.8">
@@ -21253,7 +21267,7 @@
         <v>134</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="381" ht="22.35">
@@ -21267,10 +21281,10 @@
         <v>139</v>
       </c>
       <c r="I381" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K381" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="382" ht="12.8">
@@ -21313,7 +21327,7 @@
         <v>86</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="387" ht="12.8">
@@ -21336,11 +21350,11 @@
         <v>140</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J388" s="4"/>
       <c r="K388" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L388" s="1"/>
       <c r="M388" s="1"/>
@@ -21594,10 +21608,10 @@
         <v>141</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K389" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="390" ht="12.8">
@@ -21605,10 +21619,10 @@
         <v>142</v>
       </c>
       <c r="I390" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K390" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L390" s="1"/>
       <c r="M390" s="1"/>
@@ -21862,10 +21876,10 @@
         <v>143</v>
       </c>
       <c r="I391" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K391" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="392" ht="12.8">
@@ -21873,10 +21887,10 @@
         <v>144</v>
       </c>
       <c r="I392" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K392" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="394" ht="12.8">
@@ -22418,7 +22432,7 @@
         <v>128</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="403" ht="12.8">
@@ -22426,7 +22440,7 @@
         <v>86</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" s="9" customFormat="1" ht="12.8">
@@ -22706,11 +22720,11 @@
         <v>145</v>
       </c>
       <c r="I406" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J406" s="4"/>
       <c r="K406" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L406" s="1"/>
       <c r="M406" s="1"/>
@@ -22967,10 +22981,10 @@
         <v>146</v>
       </c>
       <c r="I407" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K407" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L407" s="1"/>
       <c r="M407" s="1"/>
@@ -23227,10 +23241,10 @@
         <v>147</v>
       </c>
       <c r="I408" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K408" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L408" s="1"/>
       <c r="M408" s="1"/>
@@ -23487,10 +23501,10 @@
         <v>148</v>
       </c>
       <c r="I409" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K409" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="410" ht="74.6">
@@ -23501,10 +23515,10 @@
         <v>149</v>
       </c>
       <c r="I410" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K410" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="411" ht="12.8">
@@ -23515,10 +23529,10 @@
         <v>150</v>
       </c>
       <c r="I411" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K411" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="412" ht="12.8">
@@ -23529,10 +23543,10 @@
         <v>151</v>
       </c>
       <c r="I412" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K412" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="413" ht="12.8">
@@ -23543,10 +23557,10 @@
         <v>152</v>
       </c>
       <c r="I413" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K413" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="414" ht="12.8">
@@ -23557,10 +23571,10 @@
         <v>153</v>
       </c>
       <c r="I414" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K414" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="415" ht="12.8">
@@ -23568,7 +23582,7 @@
         <v>86</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="416" ht="12.8">
@@ -24110,10 +24124,10 @@
         <v>154</v>
       </c>
       <c r="I420" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K420" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="421" ht="12.8">
@@ -24121,10 +24135,10 @@
         <v>155</v>
       </c>
       <c r="I421" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K421" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="422" ht="12.8">
@@ -24140,7 +24154,7 @@
         <v>128</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="424" ht="12.8">
@@ -24164,10 +24178,10 @@
         <v>156</v>
       </c>
       <c r="I427" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K427" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="429" ht="12.8">
@@ -24178,10 +24192,10 @@
         <v>157</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K429" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="430" ht="12.8">
@@ -24192,10 +24206,10 @@
         <v>158</v>
       </c>
       <c r="I430" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K430" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="432" ht="12.8">
@@ -24235,10 +24249,10 @@
         <v>159</v>
       </c>
       <c r="I436" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K436" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="437" ht="12.8">
@@ -24254,7 +24268,7 @@
         <v>128</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="439" ht="12.8">
@@ -24281,10 +24295,10 @@
         <v>160</v>
       </c>
       <c r="I442" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K442" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="443" ht="12.8">
@@ -24295,10 +24309,10 @@
         <v>161</v>
       </c>
       <c r="I443" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="K443" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="444" ht="12.8">
@@ -24309,10 +24323,10 @@
         <v>162</v>
       </c>
       <c r="I444" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K444" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="446" ht="12.8">
@@ -24352,10 +24366,10 @@
         <v>163</v>
       </c>
       <c r="I450" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K450" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="451" ht="32.8">
@@ -24363,10 +24377,10 @@
         <v>164</v>
       </c>
       <c r="I451" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K451" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="452" ht="12.8">
@@ -24374,10 +24388,10 @@
         <v>165</v>
       </c>
       <c r="I452" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="K452" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="453" ht="12.8">
@@ -24393,10 +24407,10 @@
         <v>166</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K454" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="456" ht="12.8">
@@ -24404,10 +24418,10 @@
         <v>167</v>
       </c>
       <c r="I456" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="K456" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="457" ht="12.8">
@@ -24415,10 +24429,10 @@
         <v>168</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K457" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="460" ht="12.8">
@@ -24426,7 +24440,7 @@
         <v>86</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="461" ht="12.8">
@@ -24434,10 +24448,10 @@
         <v>169</v>
       </c>
       <c r="I461" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="K461" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="462" s="9" customFormat="1" ht="12.8">
@@ -24708,7 +24722,7 @@
         <v>128</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="464" ht="12.8">
@@ -24719,7 +24733,7 @@
         <v>86</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K464" s="1"/>
       <c r="L464" s="1"/>
@@ -25754,10 +25768,10 @@
         <v>170</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K469" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L469" s="1"/>
       <c r="M469" s="1"/>
@@ -26014,10 +26028,10 @@
         <v>171</v>
       </c>
       <c r="I470" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K470" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="471" ht="12.8">
@@ -26028,10 +26042,10 @@
         <v>172</v>
       </c>
       <c r="I471" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K471" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="472" ht="12.8">
@@ -26042,10 +26056,10 @@
         <v>173</v>
       </c>
       <c r="I472" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K472" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="473" ht="12.8">
@@ -26056,10 +26070,10 @@
         <v>174</v>
       </c>
       <c r="I473" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K473" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="474" ht="12.8">
@@ -26070,10 +26084,10 @@
         <v>175</v>
       </c>
       <c r="I474" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K474" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="476" ht="12.8">
@@ -26081,7 +26095,7 @@
         <v>102</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="477" ht="12.8">
@@ -26089,7 +26103,7 @@
         <v>128</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="478" ht="12.8">
@@ -26097,7 +26111,7 @@
         <v>86</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="480" s="9" customFormat="1" ht="12.8">
@@ -26377,11 +26391,11 @@
         <v>176</v>
       </c>
       <c r="I481" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J481" s="4"/>
       <c r="K481" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L481" s="1"/>
       <c r="M481" s="1"/>
@@ -26638,10 +26652,10 @@
         <v>177</v>
       </c>
       <c r="I482" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K482" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L482" s="1"/>
       <c r="M482" s="1"/>
@@ -27742,7 +27756,7 @@
         <v>61</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" ht="12.8">
@@ -27750,7 +27764,7 @@
         <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" ht="12.8">
@@ -27758,12 +27772,12 @@
         <v>61</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" ht="12.8">
       <c r="D9" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" ht="12.8">
@@ -27805,7 +27819,7 @@
         <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -28322,10 +28336,10 @@
     </row>
     <row r="21" ht="12.8">
       <c r="I21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" ht="12.8">
@@ -28581,15 +28595,15 @@
         <v>128</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" ht="12.8">
       <c r="I25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" ht="12.8">
@@ -28642,7 +28656,7 @@
         <v>86</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -29159,10 +29173,10 @@
     </row>
     <row r="39" ht="12.8">
       <c r="I39" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" ht="12.8">
@@ -29452,7 +29466,7 @@
         <v>86</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -30216,13 +30230,13 @@
         <v>1</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K54" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" ht="12.8">
@@ -30484,13 +30498,13 @@
         <v>2</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K56" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="57" ht="64.15">
@@ -30498,13 +30512,13 @@
         <v>3</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J57" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K57" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="58" ht="12.8">
@@ -30520,13 +30534,13 @@
         <v>4</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K59" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="60" ht="32.8">
@@ -30534,13 +30548,13 @@
         <v>5</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J60" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K60" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" ht="22.35">
@@ -30548,13 +30562,13 @@
         <v>6</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J61" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K61" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="62" ht="12.8">
@@ -30570,13 +30584,13 @@
         <v>7</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K63" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="64" ht="53.7">
@@ -30584,13 +30598,13 @@
         <v>8</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K64" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="65" ht="22.35">
@@ -30598,13 +30612,13 @@
         <v>9</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K65" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="66" ht="43.25">
@@ -30612,13 +30626,13 @@
         <v>10</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J66" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K66" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="68" ht="12.8">
@@ -30665,7 +30679,7 @@
         <v>86</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -31429,13 +31443,13 @@
         <v>31</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K82" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" ht="12.8">
@@ -31697,13 +31711,13 @@
         <v>32</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K84" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="86" ht="12.8">
@@ -31756,7 +31770,7 @@
         <v>86</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -32018,10 +32032,10 @@
         <v>11</v>
       </c>
       <c r="I99" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K99" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="100" ht="43.25">
@@ -32029,10 +32043,10 @@
         <v>12</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K100" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="101" ht="22.35">
@@ -32040,10 +32054,10 @@
         <v>13</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K101" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="102" ht="12.8">
@@ -32059,10 +32073,10 @@
         <v>14</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K103" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="104" ht="32.8">
@@ -32070,10 +32084,10 @@
         <v>15</v>
       </c>
       <c r="I104" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K104" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="105" s="9" customFormat="1" ht="22.35">
@@ -32088,11 +32102,11 @@
         <v>16</v>
       </c>
       <c r="I105" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
@@ -32345,10 +32359,10 @@
         <v>17</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -32609,10 +32623,10 @@
         <v>18</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -32873,10 +32887,10 @@
         <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K110" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" ht="32.8">
@@ -32884,10 +32898,10 @@
         <v>20</v>
       </c>
       <c r="I111" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="K111" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="112" ht="32.8">
@@ -32895,10 +32909,10 @@
         <v>21</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K112" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="113" ht="22.35">
@@ -32906,10 +32920,10 @@
         <v>22</v>
       </c>
       <c r="I113" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K113" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="114" ht="32.8">
@@ -32917,10 +32931,10 @@
         <v>23</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K114" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="115" ht="32.8">
@@ -32928,10 +32942,10 @@
         <v>24</v>
       </c>
       <c r="I115" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K115" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L115" s="1"/>
     </row>
@@ -32940,10 +32954,10 @@
         <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K116" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="117" ht="12.8">
@@ -32959,10 +32973,10 @@
         <v>26</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="K118" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="119" ht="32.8">
@@ -32970,10 +32984,10 @@
         <v>27</v>
       </c>
       <c r="I119" s="10" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K119" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="120" ht="32.8">
@@ -32981,10 +32995,10 @@
         <v>28</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K120" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="121" ht="32.8">
@@ -32992,10 +33006,10 @@
         <v>29</v>
       </c>
       <c r="I121" s="10" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K121" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="122" ht="32.8">
@@ -33003,10 +33017,10 @@
         <v>30</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K122" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="123" ht="12.8">
@@ -33038,7 +33052,7 @@
         <v>86</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -33297,7 +33311,7 @@
     </row>
     <row r="128" ht="12.8">
       <c r="D128" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="129" ht="12.8">
@@ -34093,7 +34107,7 @@
         <v>86</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="1"/>
@@ -34352,7 +34366,7 @@
     </row>
     <row r="143" ht="12.8">
       <c r="D143" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="144" ht="12.8">

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_main.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Dialog/Drama/_main.xlsx
@@ -699,7 +699,7 @@
   </si>
   <si>
     <t xml:space="preserve">Aha! That is a funny joke, Father.
-You probably know the incident in which a village disappeared because of a silly attempt to frighten a Dreaming Child. I cannot take my eyes off Elminare for even a moment, the girl is so terribly easily frightened. 
+You probably know the incident in which a village disappeared because of a silly attempt to frighten a Dreaming Child. I cannot take my eyes off Eluminaire for even a moment, the girl is so terribly easily frightened. 
 Oh, if only she was half as beautiful as the late Lady Friaune, this would be much more enjoyable.</t>
   </si>
   <si>
@@ -763,7 +763,7 @@
     <t xml:space="preserve">メルヴィン、お前さんの周りはいつも華やかだな。今日は新曲を携えてきたぞ。御婦人方もゆっくり聴いていってくれ。</t>
   </si>
   <si>
-    <t xml:space="preserve">Melvin, it' s always a spectacle around you. I've got a new song for you today. Ladies, please take your time and listen.</t>
+    <t xml:space="preserve">Melvin, it's always a spectacle around you. I've got a new song for you today. Ladies, please take your time and listen.</t>
   </si>
   <si>
     <t xml:space="preserve">ギャア゛ア゛ー</t>
@@ -2489,7 +2489,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -2528,6 +2528,10 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -7499,7 +7503,7 @@
       <c r="I104" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="J104" s="6" t="s">
+      <c r="J104" s="10" t="s">
         <v>168</v>
       </c>
       <c r="K104" t="s">
@@ -8732,7 +8736,7 @@
       <c r="I125" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="J125" s="6" t="s">
+      <c r="J125" s="10" t="s">
         <v>191</v>
       </c>
       <c r="K125" t="s">
@@ -30497,10 +30501,10 @@
       <c r="H56" s="1">
         <v>2</v>
       </c>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="J56" s="10" t="s">
+      <c r="J56" s="11" t="s">
         <v>450</v>
       </c>
       <c r="K56" t="s">
@@ -30511,10 +30515,10 @@
       <c r="H57" s="1">
         <v>3</v>
       </c>
-      <c r="I57" s="10" t="s">
+      <c r="I57" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="J57" s="10" t="s">
+      <c r="J57" s="11" t="s">
         <v>452</v>
       </c>
       <c r="K57" t="s">
@@ -30533,10 +30537,10 @@
       <c r="H59" s="1">
         <v>4</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="J59" s="10" t="s">
+      <c r="J59" s="11" t="s">
         <v>454</v>
       </c>
       <c r="K59" t="s">
@@ -30547,10 +30551,10 @@
       <c r="H60" s="1">
         <v>5</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="J60" s="10" t="s">
+      <c r="J60" s="11" t="s">
         <v>456</v>
       </c>
       <c r="K60" t="s">
@@ -30561,10 +30565,10 @@
       <c r="H61" s="1">
         <v>6</v>
       </c>
-      <c r="I61" s="10" t="s">
+      <c r="I61" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="J61" s="10" t="s">
+      <c r="J61" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K61" t="s">
@@ -30583,10 +30587,10 @@
       <c r="H63" s="1">
         <v>7</v>
       </c>
-      <c r="I63" s="10" t="s">
+      <c r="I63" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="J63" s="10" t="s">
+      <c r="J63" s="11" t="s">
         <v>460</v>
       </c>
       <c r="K63" t="s">
@@ -30597,10 +30601,10 @@
       <c r="H64" s="1">
         <v>8</v>
       </c>
-      <c r="I64" s="10" t="s">
+      <c r="I64" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="J64" s="10" t="s">
+      <c r="J64" s="11" t="s">
         <v>462</v>
       </c>
       <c r="K64" t="s">
@@ -30611,10 +30615,10 @@
       <c r="H65" s="1">
         <v>9</v>
       </c>
-      <c r="I65" s="10" t="s">
+      <c r="I65" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="J65" s="10" t="s">
+      <c r="J65" s="11" t="s">
         <v>464</v>
       </c>
       <c r="K65" t="s">
@@ -30625,10 +30629,10 @@
       <c r="H66" s="1">
         <v>10</v>
       </c>
-      <c r="I66" s="10" t="s">
+      <c r="I66" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="J66" s="10" t="s">
+      <c r="J66" s="11" t="s">
         <v>466</v>
       </c>
       <c r="K66" t="s">
@@ -32031,7 +32035,7 @@
       <c r="H99" s="1">
         <v>11</v>
       </c>
-      <c r="I99" s="10" t="s">
+      <c r="I99" s="11" t="s">
         <v>469</v>
       </c>
       <c r="K99" t="s">
@@ -32042,7 +32046,7 @@
       <c r="H100" s="1">
         <v>12</v>
       </c>
-      <c r="I100" s="10" t="s">
+      <c r="I100" s="11" t="s">
         <v>470</v>
       </c>
       <c r="K100" t="s">
@@ -32053,7 +32057,7 @@
       <c r="H101" s="1">
         <v>13</v>
       </c>
-      <c r="I101" s="10" t="s">
+      <c r="I101" s="11" t="s">
         <v>471</v>
       </c>
       <c r="K101" t="s">
@@ -32072,7 +32076,7 @@
       <c r="H103" s="1">
         <v>14</v>
       </c>
-      <c r="I103" s="10" t="s">
+      <c r="I103" s="11" t="s">
         <v>472</v>
       </c>
       <c r="K103" t="s">
@@ -32083,7 +32087,7 @@
       <c r="H104" s="1">
         <v>15</v>
       </c>
-      <c r="I104" s="10" t="s">
+      <c r="I104" s="11" t="s">
         <v>473</v>
       </c>
       <c r="K104" t="s">
@@ -32101,7 +32105,7 @@
       <c r="H105" s="1">
         <v>16</v>
       </c>
-      <c r="I105" s="10" t="s">
+      <c r="I105" s="11" t="s">
         <v>474</v>
       </c>
       <c r="J105" s="1"/>
@@ -32358,7 +32362,7 @@
       <c r="H106" s="1">
         <v>17</v>
       </c>
-      <c r="I106" s="10" t="s">
+      <c r="I106" s="11" t="s">
         <v>475</v>
       </c>
       <c r="K106" s="1" t="s">
@@ -32622,7 +32626,7 @@
       <c r="H108" s="1">
         <v>18</v>
       </c>
-      <c r="I108" s="10" t="s">
+      <c r="I108" s="11" t="s">
         <v>476</v>
       </c>
       <c r="K108" s="1" t="s">
@@ -32897,7 +32901,7 @@
       <c r="H111" s="1">
         <v>20</v>
       </c>
-      <c r="I111" s="10" t="s">
+      <c r="I111" s="11" t="s">
         <v>478</v>
       </c>
       <c r="K111" t="s">
@@ -32908,7 +32912,7 @@
       <c r="H112" s="1">
         <v>21</v>
       </c>
-      <c r="I112" s="10" t="s">
+      <c r="I112" s="11" t="s">
         <v>479</v>
       </c>
       <c r="K112" t="s">
@@ -32919,7 +32923,7 @@
       <c r="H113" s="1">
         <v>22</v>
       </c>
-      <c r="I113" s="10" t="s">
+      <c r="I113" s="11" t="s">
         <v>480</v>
       </c>
       <c r="K113" t="s">
@@ -32930,7 +32934,7 @@
       <c r="H114" s="1">
         <v>23</v>
       </c>
-      <c r="I114" s="10" t="s">
+      <c r="I114" s="11" t="s">
         <v>481</v>
       </c>
       <c r="K114" t="s">
@@ -32941,7 +32945,7 @@
       <c r="H115" s="1">
         <v>24</v>
       </c>
-      <c r="I115" s="10" t="s">
+      <c r="I115" s="11" t="s">
         <v>482</v>
       </c>
       <c r="K115" t="s">
@@ -32972,7 +32976,7 @@
       <c r="H118" s="1">
         <v>26</v>
       </c>
-      <c r="I118" s="10" t="s">
+      <c r="I118" s="11" t="s">
         <v>484</v>
       </c>
       <c r="K118" t="s">
@@ -32983,7 +32987,7 @@
       <c r="H119" s="1">
         <v>27</v>
       </c>
-      <c r="I119" s="10" t="s">
+      <c r="I119" s="11" t="s">
         <v>485</v>
       </c>
       <c r="K119" t="s">
@@ -32994,7 +32998,7 @@
       <c r="H120" s="1">
         <v>28</v>
       </c>
-      <c r="I120" s="10" t="s">
+      <c r="I120" s="11" t="s">
         <v>486</v>
       </c>
       <c r="K120" t="s">
@@ -33005,7 +33009,7 @@
       <c r="H121" s="1">
         <v>29</v>
       </c>
-      <c r="I121" s="10" t="s">
+      <c r="I121" s="11" t="s">
         <v>487</v>
       </c>
       <c r="K121" t="s">
@@ -33016,7 +33020,7 @@
       <c r="H122" s="1">
         <v>30</v>
       </c>
-      <c r="I122" s="10" t="s">
+      <c r="I122" s="11" t="s">
         <v>488</v>
       </c>
       <c r="K122" t="s">
